--- a/outputs/официальный_вывоз_2склада_парето_31.07.2026.xlsx
+++ b/outputs/официальный_вывоз_2склада_парето_31.07.2026.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,10 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
@@ -51,7 +55,7 @@
       <color rgb="00808080"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +80,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,7 +147,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -510,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N114"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6128,6 +6145,133 @@
         <v>1941512</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>ИТОГИ ПО ЦВЕТАМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Зона</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Остаток, шт</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Себест.сумма, ₽</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>Затраты, ₽</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Ср. окупаемость, ×</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="16" t="inlineStr">
+        <is>
+          <t>🟢 Действовать (себест.≥2×затрат)</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>2535</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>1901244</v>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>650754</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Опционально (1–2×)</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="C119" s="8" t="n">
+        <v>3378</v>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>1372229</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>893003</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="18" t="inlineStr">
+        <is>
+          <t>🔴 НЕ трогать (затраты&gt;себест.)</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="C120" s="11" t="n">
+        <v>1572</v>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>288808</v>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>397755</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="19" t="inlineStr">
+        <is>
+          <t>ВСЕГО</t>
+        </is>
+      </c>
+      <c r="B121" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="C121" s="20" t="n">
+        <v>7485</v>
+      </c>
+      <c r="D121" s="20" t="n">
+        <v>3562281</v>
+      </c>
+      <c r="E121" s="20" t="n">
+        <v>1941512</v>
+      </c>
+      <c r="F121" s="20" t="n">
+        <v>1.83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6139,7 +6283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8707,6 +8851,133 @@
         <v>1425421</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>ИТОГИ ПО ЦВЕТАМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Зона</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Остаток, шт</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Себест.сумма, ₽</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Затраты, ₽</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Ср. окупаемость, ×</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>🟢 Действовать (себест.≥2×затрат)</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>1584</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>1107288</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>396619</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>🟡 Опционально (1–2×)</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C58" s="8" t="n">
+        <v>2435</v>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>910910</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>606738</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>🔴 НЕ трогать (затраты&gt;себест.)</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>1705</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>327967</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>422064</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>ВСЕГО</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="n">
+        <v>49</v>
+      </c>
+      <c r="C60" s="20" t="n">
+        <v>5724</v>
+      </c>
+      <c r="D60" s="20" t="n">
+        <v>2346164</v>
+      </c>
+      <c r="E60" s="20" t="n">
+        <v>1425421</v>
+      </c>
+      <c r="F60" s="20" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8718,46 +8989,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>Официальный вывоз — итоги по фирмам</t>
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Официальный вывоз — итоги</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Тариф WB: Коледино 245/272 ₽, Казань 256/287 ₽. От цены и налога не зависит.</t>
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>Тариф WB: Коледино 245/272 ₽, Казань 256/287 ₽. От цены/налога не зависит.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>ВСЕ</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Коротич</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>КРОНА</t>
         </is>
@@ -8769,13 +9040,13 @@
           <t>SKU</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="24" t="n">
         <v>159</v>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="24" t="n">
         <v>110</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="24" t="n">
         <v>49</v>
       </c>
     </row>
@@ -8785,13 +9056,13 @@
           <t>Остаток, шт</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="24" t="n">
         <v>13209</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="24" t="n">
         <v>7485</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="24" t="n">
         <v>5724</v>
       </c>
     </row>
@@ -8801,17 +9072,17 @@
           <t>Себестоимость, ₽</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>5 908 446</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>3 562 281</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>2 346 164</t>
         </is>
@@ -8823,17 +9094,17 @@
           <t>Полный вывоз, ₽</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>3 366 933</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>1 941 512</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>1 425 421</t>
         </is>
@@ -8842,36 +9113,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Парето SKU</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="n">
+          <t>🟢 SKU (≥2×)</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="n">
         <v>58</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="24" t="n">
         <v>42</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="24" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Парето: освобождаем ₽</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+          <t>🟢 освобождаем, ₽</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>3 008 532</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>1 901 244</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>1 107 288</t>
         </is>
@@ -8880,22 +9151,76 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Парето: затраты ₽</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
+          <t>🟢 затраты, ₽</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>1 047 373</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>650 754</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>396 619</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>🟡 SKU (1–2×)</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>🔴 SKU (&lt;1×)</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>41</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>🔴 себест., ₽</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>616 775</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>288 808</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>327 967</t>
         </is>
       </c>
     </row>
